--- a/templates/Migration_Checklist.xlsx
+++ b/templates/Migration_Checklist.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="82" documentId="11_21B7E1DEFAA0860C78C7A782675AE3FEF7CFE12E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E2D183E-E7BE-454F-8F60-8FFF60DB6C6A}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="11_21B7E1DEFAA0860C78C7A782675AE3FEF7CFE12E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EA5CBEA-B661-44C5-B552-84EA57FB67AA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1027,6 +1027,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1039,11 +1040,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1360,43 +1360,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="36" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
     </row>
     <row r="2" spans="1:9" ht="21.95" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
     </row>
     <row r="3" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="1:9" ht="6" customHeight="1"/>
     <row r="5" spans="1:9" ht="32.1" customHeight="1">
@@ -1432,14 +1432,14 @@
       <c r="A6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
     </row>
     <row r="7" spans="1:9" ht="42" customHeight="1">
       <c r="A7" s="2">
@@ -1590,14 +1590,14 @@
       <c r="A12" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
     </row>
     <row r="13" spans="1:9" ht="42" customHeight="1">
       <c r="A13" s="8">
@@ -1806,14 +1806,14 @@
       <c r="A20" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
     </row>
     <row r="21" spans="1:9" ht="42" customHeight="1">
       <c r="A21" s="8">
@@ -2109,14 +2109,14 @@
       <c r="A31" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
     </row>
     <row r="32" spans="1:9" ht="42" customHeight="1">
       <c r="A32" s="13">
@@ -2267,14 +2267,14 @@
       <c r="A37" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
     </row>
     <row r="38" spans="1:9" ht="42" customHeight="1">
       <c r="A38" s="13">
@@ -2483,14 +2483,14 @@
       <c r="A45" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
     </row>
     <row r="46" spans="1:9" ht="42" customHeight="1">
       <c r="A46" s="13">
@@ -2641,14 +2641,14 @@
       <c r="A51" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="B51" s="33"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
     </row>
     <row r="52" spans="1:9" ht="42" customHeight="1">
       <c r="A52" s="8">
@@ -2828,14 +2828,14 @@
       <c r="A58" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="B58" s="33"/>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-      <c r="F58" s="33"/>
-      <c r="G58" s="33"/>
-      <c r="H58" s="33"/>
-      <c r="I58" s="33"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
     </row>
     <row r="59" spans="1:9" ht="42" customHeight="1">
       <c r="A59" s="2">
@@ -2986,14 +2986,14 @@
       <c r="A64" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="33"/>
-      <c r="F64" s="33"/>
-      <c r="G64" s="33"/>
-      <c r="H64" s="33"/>
-      <c r="I64" s="33"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
     </row>
     <row r="65" spans="1:9" ht="42" customHeight="1">
       <c r="A65" s="2">
@@ -3127,7 +3127,7 @@
     <mergeCell ref="A20:I20"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G68" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="G7:G11 G13 G14 G15:G18 G19 G21:G24 G25:G28 G29:G30 G32:G36 G38:G41 G42:G44 G46:G50 G52:G56 G57 G59:G62 G63 G65:G66 G67:G68" xr:uid="{8BE94A50-EB6B-4A53-A6A2-2C928F263579}">
       <formula1>"Not Started,In Progress,Complete,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3145,16 +3145,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="27.95" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="B1" s="33"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:2" ht="24" customHeight="1">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="B2" s="34"/>
+      <c r="B2" s="33"/>
     </row>
     <row r="3" spans="1:2" ht="24" customHeight="1">
       <c r="A3" s="19" t="s">
@@ -3190,10 +3190,10 @@
     </row>
     <row r="7" spans="1:2" ht="24" customHeight="1"/>
     <row r="8" spans="1:2" ht="24" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
     </row>
     <row r="9" spans="1:2" ht="24" customHeight="1">
       <c r="A9" s="23" t="s">
@@ -3229,10 +3229,10 @@
     </row>
     <row r="13" spans="1:2" ht="24" customHeight="1"/>
     <row r="14" spans="1:2" ht="24" customHeight="1">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="B14" s="34"/>
+      <c r="B14" s="33"/>
     </row>
     <row r="15" spans="1:2" ht="24" customHeight="1">
       <c r="A15" s="19" t="s">
